--- a/www/flightdata/xlsx/eoss-374.xlsx
+++ b/www/flightdata/xlsx/eoss-374.xlsx
@@ -3363,7 +3363,7 @@
         <v>27397.25</v>
       </c>
       <c r="I2">
-        <v>670</v>
+        <v>424</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
